--- a/EnergyScope_LCA-ANNE_20_02_25/case_studies/SA_FINAL_03-03-2025/2035_steamlow5/output/LCA_Resources_final.xlsx
+++ b/EnergyScope_LCA-ANNE_20_02_25/case_studies/SA_FINAL_03-03-2025/2035_steamlow5/output/LCA_Resources_final.xlsx
@@ -522,52 +522,52 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.255218390216273e-06</v>
+        <v>1.321176986093592e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>0.001467999999999994</v>
+        <v>8.599999999997294e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01129548844330029</v>
+        <v>0.0006617247998116644</v>
       </c>
       <c r="E2" t="n">
-        <v>3.965892717480413e-08</v>
+        <v>2.323343145117232e-09</v>
       </c>
       <c r="F2" t="n">
-        <v>5.724148580399519e-07</v>
+        <v>3.353384045737097e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>5.243780075516253e-06</v>
+        <v>3.071969254048077e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>4.008447928758935e-13</v>
+        <v>2.34827330976268e-14</v>
       </c>
       <c r="I2" t="n">
-        <v>6.855614728190506e-12</v>
+        <v>4.016232061472756e-13</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0001203477958347648</v>
+        <v>7.050347712388667e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>0.002087629739798466</v>
+        <v>0.0001222998348927877</v>
       </c>
       <c r="L2" t="n">
-        <v>9.008206350467725e-09</v>
+        <v>5.277287099046212e-10</v>
       </c>
       <c r="M2" t="n">
-        <v>1.49064866621441e-11</v>
+        <v>8.732682921961814e-13</v>
       </c>
       <c r="N2" t="n">
-        <v>2.944924213546309e-06</v>
+        <v>1.725228081504795e-07</v>
       </c>
       <c r="O2" t="n">
-        <v>0.001422049937948769</v>
+        <v>8.330810263185024e-05</v>
       </c>
       <c r="P2" t="n">
-        <v>0.02675400913740635</v>
+        <v>0.001567332960365281</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.017758017926993e-10</v>
+        <v>1.182065323853321e-11</v>
       </c>
     </row>
     <row r="3">
@@ -632,52 +632,52 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>31.68992590411957</v>
+        <v>31.68994192626272</v>
       </c>
       <c r="C4" t="n">
-        <v>773.352286</v>
+        <v>773.352677</v>
       </c>
       <c r="D4" t="n">
-        <v>28014.19299153017</v>
+        <v>28014.20715525563</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1169215093323459</v>
+        <v>0.1169215684468154</v>
       </c>
       <c r="F4" t="n">
-        <v>3.505137474365867</v>
+        <v>3.50513924653203</v>
       </c>
       <c r="G4" t="n">
-        <v>117.489934618621</v>
+        <v>117.4899940204813</v>
       </c>
       <c r="H4" t="n">
-        <v>1.076720844585766e-06</v>
+        <v>1.076721388966197e-06</v>
       </c>
       <c r="I4" t="n">
-        <v>1.928515948964504e-05</v>
+        <v>1.928516924004922e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>190.5197759176698</v>
+        <v>190.5198722427647</v>
       </c>
       <c r="K4" t="n">
-        <v>44004.15169933929</v>
+        <v>44004.17394744488</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02652653560197257</v>
+        <v>0.02652654901355176</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0001656451528323169</v>
+        <v>0.0001656452365810249</v>
       </c>
       <c r="N4" t="n">
-        <v>8.400693151423132</v>
+        <v>8.400697398738465</v>
       </c>
       <c r="O4" t="n">
-        <v>6224.458161003861</v>
+        <v>6224.461308034245</v>
       </c>
       <c r="P4" t="n">
-        <v>7950.517482954949</v>
+        <v>7950.52150266549</v>
       </c>
       <c r="Q4" t="n">
-        <v>8.771579091597727e-05</v>
+        <v>8.771583526429674e-05</v>
       </c>
     </row>
     <row r="5">
@@ -687,52 +687,52 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.347053996974085e-06</v>
+        <v>2.143040449731681e-07</v>
       </c>
       <c r="C5" t="n">
-        <v>-4.399999999999625e-05</v>
+        <v>-6.999999999999999e-06</v>
       </c>
       <c r="D5" t="n">
-        <v>0.007427441481325776</v>
+        <v>0.001181638417483747</v>
       </c>
       <c r="E5" t="n">
-        <v>1.393138004573795e-08</v>
+        <v>2.216355916367589e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>1.150893245981586e-06</v>
+        <v>1.830966527698133e-07</v>
       </c>
       <c r="G5" t="n">
-        <v>5.523970227128772e-06</v>
+        <v>8.788134452251068e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>7.827343043404932e-14</v>
+        <v>1.2452591205418e-14</v>
       </c>
       <c r="I5" t="n">
-        <v>3.809891774822203e-12</v>
+        <v>6.06119145994493e-13</v>
       </c>
       <c r="J5" t="n">
-        <v>3.800273430913388e-06</v>
+        <v>6.045889549180904e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01423584531224108</v>
+        <v>0.002264793572402182</v>
       </c>
       <c r="L5" t="n">
-        <v>9.122136655067096e-10</v>
+        <v>1.451249013306252e-10</v>
       </c>
       <c r="M5" t="n">
-        <v>1.036083144406096e-11</v>
+        <v>1.648314093373474e-12</v>
       </c>
       <c r="N5" t="n">
-        <v>2.171803074441403e-07</v>
+        <v>3.455141254793436e-08</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0006454607127276754</v>
+        <v>0.0001026869315703207</v>
       </c>
       <c r="P5" t="n">
-        <v>0.000703067869319068</v>
+        <v>0.0001118517064825885</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.044283810495363e-11</v>
+        <v>1.6613606076064e-12</v>
       </c>
     </row>
     <row r="6">
@@ -797,52 +797,52 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.090403655779972e-06</v>
+        <v>3.618006327310508e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>-5.199999999999519e-05</v>
+        <v>-8.999999999996724e-06</v>
       </c>
       <c r="D7" t="n">
-        <v>0.00827845263555939</v>
+        <v>0.001432809110000274</v>
       </c>
       <c r="E7" t="n">
-        <v>2.448268405416869e-08</v>
+        <v>4.237387624758815e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>1.931926059670792e-06</v>
+        <v>3.343718180198539e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>8.38319094437442e-06</v>
+        <v>1.450936894218255e-06</v>
       </c>
       <c r="H7" t="n">
-        <v>1.104927109680622e-13</v>
+        <v>1.91237384367748e-14</v>
       </c>
       <c r="I7" t="n">
-        <v>6.668589781916948e-12</v>
+        <v>1.154179000716081e-12</v>
       </c>
       <c r="J7" t="n">
-        <v>8.955583834994054e-06</v>
+        <v>1.55000489451778e-06</v>
       </c>
       <c r="K7" t="n">
-        <v>0.02187338820687472</v>
+        <v>0.003785778728111904</v>
       </c>
       <c r="L7" t="n">
-        <v>1.483878079350433e-09</v>
+        <v>2.568250521951975e-10</v>
       </c>
       <c r="M7" t="n">
-        <v>1.756819126430875e-11</v>
+        <v>3.040648488052612e-12</v>
       </c>
       <c r="N7" t="n">
-        <v>4.039158437326292e-07</v>
+        <v>6.990851141524375e-08</v>
       </c>
       <c r="O7" t="n">
-        <v>0.00109315305202892</v>
+        <v>0.0001891995666972616</v>
       </c>
       <c r="P7" t="n">
-        <v>0.001566124711321819</v>
+        <v>0.0002710600461902412</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.709036451155233e-11</v>
+        <v>2.957947703921715e-12</v>
       </c>
     </row>
     <row r="8">
@@ -1072,52 +1072,52 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>8.788980827218994</v>
+        <v>8.354320400888572</v>
       </c>
       <c r="C12" t="n">
-        <v>833.8012360000001</v>
+        <v>792.565465</v>
       </c>
       <c r="D12" t="n">
-        <v>154596.8837648145</v>
+        <v>146951.2706126657</v>
       </c>
       <c r="E12" t="n">
-        <v>4.218788526547922</v>
+        <v>4.010147677785546</v>
       </c>
       <c r="F12" t="n">
-        <v>3.495408006097866</v>
+        <v>3.322542054516309</v>
       </c>
       <c r="G12" t="n">
-        <v>31.0238296119136</v>
+        <v>29.48954124894949</v>
       </c>
       <c r="H12" t="n">
-        <v>1.096875315108318e-06</v>
+        <v>1.042629174233853e-06</v>
       </c>
       <c r="I12" t="n">
-        <v>5.731959788525174e-05</v>
+        <v>5.448484817494028e-05</v>
       </c>
       <c r="J12" t="n">
-        <v>40.76958766142239</v>
+        <v>38.75332130442357</v>
       </c>
       <c r="K12" t="n">
-        <v>16369.46783014676</v>
+        <v>15559.91322925168</v>
       </c>
       <c r="L12" t="n">
-        <v>0.003206288426142602</v>
+        <v>0.003047720928768003</v>
       </c>
       <c r="M12" t="n">
-        <v>5.296856737690811e-05</v>
+        <v>5.034899856332547e-05</v>
       </c>
       <c r="N12" t="n">
-        <v>7.317107808922105</v>
+        <v>6.955239093737059</v>
       </c>
       <c r="O12" t="n">
-        <v>237.5191185773792</v>
+        <v>225.7725732870833</v>
       </c>
       <c r="P12" t="n">
-        <v>88060.42123396505</v>
+        <v>83705.37927985679</v>
       </c>
       <c r="Q12" t="n">
-        <v>6.818160498980298e-05</v>
+        <v>6.480967301323299e-05</v>
       </c>
     </row>
     <row r="13">
@@ -1127,52 +1127,52 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>7.014158434758514</v>
+        <v>7.014158703848826</v>
       </c>
       <c r="C13" t="n">
-        <v>521.3237420000002</v>
+        <v>521.3237620000001</v>
       </c>
       <c r="D13" t="n">
-        <v>32348.14589413129</v>
+        <v>32348.14713513158</v>
       </c>
       <c r="E13" t="n">
-        <v>0.01715554040884814</v>
+        <v>0.01715554106700118</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9182273145933071</v>
+        <v>0.9182273498200669</v>
       </c>
       <c r="G13" t="n">
-        <v>9.488091160561245</v>
+        <v>9.488091524561208</v>
       </c>
       <c r="H13" t="n">
-        <v>2.511386090717747e-07</v>
+        <v>2.511386187064254e-07</v>
       </c>
       <c r="I13" t="n">
-        <v>7.246381642926166e-06</v>
+        <v>7.246381920925461e-06</v>
       </c>
       <c r="J13" t="n">
-        <v>271.3824319242356</v>
+        <v>271.3824423355179</v>
       </c>
       <c r="K13" t="n">
-        <v>9082.400903192884</v>
+        <v>9082.401251628997</v>
       </c>
       <c r="L13" t="n">
-        <v>0.001149870801466589</v>
+        <v>0.001149870845580091</v>
       </c>
       <c r="M13" t="n">
-        <v>3.782236976520959e-05</v>
+        <v>3.782237121622234e-05</v>
       </c>
       <c r="N13" t="n">
-        <v>3.89335164884362</v>
+        <v>3.893351798207684</v>
       </c>
       <c r="O13" t="n">
-        <v>125.9210012199726</v>
+        <v>125.9210060507904</v>
       </c>
       <c r="P13" t="n">
-        <v>58948.86265287615</v>
+        <v>58948.86491438308</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.001000428582906064</v>
+        <v>0.001000428621286383</v>
       </c>
     </row>
     <row r="14">
@@ -1182,52 +1182,52 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>7.997735336008405</v>
+        <v>7.997735314214468</v>
       </c>
       <c r="C14" t="n">
-        <v>1100.911966</v>
+        <v>1100.911963</v>
       </c>
       <c r="D14" t="n">
-        <v>68390.44023854646</v>
+        <v>68390.44005218158</v>
       </c>
       <c r="E14" t="n">
-        <v>0.2881215687668257</v>
+        <v>0.2881215679816906</v>
       </c>
       <c r="F14" t="n">
-        <v>2.350320491167531</v>
+        <v>2.350320484762876</v>
       </c>
       <c r="G14" t="n">
-        <v>23.82276809732197</v>
+        <v>23.82276803240461</v>
       </c>
       <c r="H14" t="n">
-        <v>3.003047351097221e-06</v>
+        <v>3.003047342913876e-06</v>
       </c>
       <c r="I14" t="n">
-        <v>5.272470705674945e-05</v>
+        <v>5.272470691307391e-05</v>
       </c>
       <c r="J14" t="n">
-        <v>2253.249081678749</v>
+        <v>2253.249075538615</v>
       </c>
       <c r="K14" t="n">
-        <v>64161.07669115173</v>
+        <v>64161.07651631193</v>
       </c>
       <c r="L14" t="n">
-        <v>0.05886471156734636</v>
+        <v>0.05886471140693923</v>
       </c>
       <c r="M14" t="n">
-        <v>0.0001157638843857273</v>
+        <v>0.0001157638840702691</v>
       </c>
       <c r="N14" t="n">
-        <v>6.003394701825613</v>
+        <v>6.003394685466281</v>
       </c>
       <c r="O14" t="n">
-        <v>2529.299696593904</v>
+        <v>2529.299689701529</v>
       </c>
       <c r="P14" t="n">
-        <v>53422.10035668666</v>
+        <v>53422.10021111071</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.0001359554914916716</v>
+        <v>0.0001359554911211911</v>
       </c>
     </row>
     <row r="15">
@@ -1292,52 +1292,52 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>11.8401252734154</v>
+        <v>12.27957582284106</v>
       </c>
       <c r="C16" t="n">
-        <v>6068.796633</v>
+        <v>6294.042223999999</v>
       </c>
       <c r="D16" t="n">
-        <v>99604.13099056951</v>
+        <v>103300.9744848821</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1759039188216273</v>
+        <v>0.1824326566505974</v>
       </c>
       <c r="F16" t="n">
-        <v>4.47401301773305</v>
+        <v>4.640067635685012</v>
       </c>
       <c r="G16" t="n">
-        <v>46.95843316710322</v>
+        <v>48.70131246769522</v>
       </c>
       <c r="H16" t="n">
-        <v>2.776530959151613e-06</v>
+        <v>2.879582914035581e-06</v>
       </c>
       <c r="I16" t="n">
-        <v>3.213191449013267e-05</v>
+        <v>3.332450216557659e-05</v>
       </c>
       <c r="J16" t="n">
-        <v>2803.154799768838</v>
+        <v>2907.194908166126</v>
       </c>
       <c r="K16" t="n">
-        <v>10001.83849037685</v>
+        <v>10373.06035825114</v>
       </c>
       <c r="L16" t="n">
-        <v>0.009035025520254479</v>
+        <v>0.009370363773631372</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0001049380225498695</v>
+        <v>0.0001088328353664809</v>
       </c>
       <c r="N16" t="n">
-        <v>35.78880438130119</v>
+        <v>37.11711885310523</v>
       </c>
       <c r="O16" t="n">
-        <v>634.7417319503894</v>
+        <v>658.3004018468384</v>
       </c>
       <c r="P16" t="n">
-        <v>451260.4781100175</v>
+        <v>468009.1746364633</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.005599765729427377</v>
+        <v>0.005807603068106313</v>
       </c>
     </row>
     <row r="17">
@@ -1347,52 +1347,52 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>7.100462125584259</v>
+        <v>2.536765029925651</v>
       </c>
       <c r="C17" t="n">
-        <v>560.138556</v>
+        <v>200.119355</v>
       </c>
       <c r="D17" t="n">
-        <v>27522.29978593479</v>
+        <v>9832.825864745344</v>
       </c>
       <c r="E17" t="n">
-        <v>0.01968193505795461</v>
+        <v>0.007031717611222186</v>
       </c>
       <c r="F17" t="n">
-        <v>0.826806956876155</v>
+        <v>0.2953913333535443</v>
       </c>
       <c r="G17" t="n">
-        <v>8.604262543535265</v>
+        <v>3.074024189227454</v>
       </c>
       <c r="H17" t="n">
-        <v>2.704300443708678e-07</v>
+        <v>9.661589167969979e-08</v>
       </c>
       <c r="I17" t="n">
-        <v>6.851823499184342e-06</v>
+        <v>2.447934505745063e-06</v>
       </c>
       <c r="J17" t="n">
-        <v>218.3306715366928</v>
+        <v>78.00247402473009</v>
       </c>
       <c r="K17" t="n">
-        <v>7375.175049433908</v>
+        <v>2634.911055658176</v>
       </c>
       <c r="L17" t="n">
-        <v>0.001116863058207398</v>
+        <v>0.0003990189792109077</v>
       </c>
       <c r="M17" t="n">
-        <v>4.618003020495753e-05</v>
+        <v>1.649862834740592e-05</v>
       </c>
       <c r="N17" t="n">
-        <v>3.501752213646173</v>
+        <v>1.25106259310008</v>
       </c>
       <c r="O17" t="n">
-        <v>109.3776715607149</v>
+        <v>39.07709771032458</v>
       </c>
       <c r="P17" t="n">
-        <v>47485.60566973264</v>
+        <v>16965.0681543358</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.0008033429491019938</v>
+        <v>0.0002870084037173274</v>
       </c>
     </row>
     <row r="18">
@@ -1512,52 +1512,52 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.141781650192248e-09</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>3e-06</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>2.08965821378439e-05</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>5.72946445650663e-11</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>5.249878637683653e-10</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>5.508354926058038e-09</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>6.142758237505448e-16</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>1.108622905680037e-14</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>3.183109976948896e-07</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>3.536723576406611e-06</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>1.235168518521803e-11</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.797787113745337e-14</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>4.334058346643353e-09</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>2.548920524638588e-07</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>4.8765574846012e-05</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.81241461829379e-13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1622,52 +1622,52 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.082270341198396e-05</v>
+        <v>1.882988994628371e-07</v>
       </c>
       <c r="C22" t="n">
-        <v>0.001206999999999998</v>
+        <v>2.099999999999823e-05</v>
       </c>
       <c r="D22" t="n">
-        <v>0.07533563218534342</v>
+        <v>0.001310727651940415</v>
       </c>
       <c r="E22" t="n">
-        <v>4.372123363048533e-07</v>
+        <v>7.606842636620678e-09</v>
       </c>
       <c r="F22" t="n">
-        <v>1.424448137763122e-06</v>
+        <v>2.478327331650628e-08</v>
       </c>
       <c r="G22" t="n">
-        <v>1.507466630779286e-05</v>
+        <v>2.622767128944688e-07</v>
       </c>
       <c r="H22" t="n">
-        <v>3.31517231065081e-12</v>
+        <v>5.767905428638048e-14</v>
       </c>
       <c r="I22" t="n">
-        <v>7.285378568562678e-11</v>
+        <v>1.267547224024885e-12</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0003247854784537613</v>
+        <v>5.650782972268785e-06</v>
       </c>
       <c r="K22" t="n">
-        <v>0.07990745146404296</v>
+        <v>0.001390270489432281</v>
       </c>
       <c r="L22" t="n">
-        <v>1.195443199111089e-07</v>
+        <v>2.079892889919701e-09</v>
       </c>
       <c r="M22" t="n">
-        <v>7.328637288427104e-11</v>
+        <v>1.275073596163682e-12</v>
       </c>
       <c r="N22" t="n">
-        <v>4.445118391951472e-06</v>
+        <v>7.733843101157677e-08</v>
       </c>
       <c r="O22" t="n">
-        <v>0.01121295289477336</v>
+        <v>0.0001950886584840274</v>
       </c>
       <c r="P22" t="n">
-        <v>0.009005434987040883</v>
+        <v>0.0001566811389625873</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.05746704842485e-10</v>
+        <v>1.839834964119305e-12</v>
       </c>
     </row>
     <row r="23">
@@ -1677,52 +1677,52 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>7.240834607247822e-06</v>
+        <v>9.681718589728708e-07</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0005309999999999977</v>
+        <v>7.099999999999956e-05</v>
       </c>
       <c r="D23" t="n">
-        <v>0.03289821189056828</v>
+        <v>0.004398819292335863</v>
       </c>
       <c r="E23" t="n">
-        <v>1.81119986991982e-08</v>
+        <v>2.421755004977533e-09</v>
       </c>
       <c r="F23" t="n">
-        <v>9.622541182544651e-07</v>
+        <v>1.286629800302578e-07</v>
       </c>
       <c r="G23" t="n">
-        <v>9.972558576926627e-06</v>
+        <v>1.333430619513727e-06</v>
       </c>
       <c r="H23" t="n">
-        <v>2.584121403303148e-13</v>
+        <v>3.455228241704768e-14</v>
       </c>
       <c r="I23" t="n">
-        <v>7.538291901883027e-12</v>
+        <v>1.007944868236712e-12</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0002745838500617666</v>
+        <v>3.671460142068811e-05</v>
       </c>
       <c r="K23" t="n">
-        <v>0.00899467656278217</v>
+        <v>0.001202678033818329</v>
       </c>
       <c r="L23" t="n">
-        <v>1.443968396084021e-09</v>
+        <v>1.930729870470156e-10</v>
       </c>
       <c r="M23" t="n">
-        <v>4.006752206174323e-11</v>
+        <v>5.357427620308406e-12</v>
       </c>
       <c r="N23" t="n">
-        <v>4.042128045051118e-06</v>
+        <v>5.404728647808454e-07</v>
       </c>
       <c r="O23" t="n">
-        <v>0.0001263891355112881</v>
+        <v>1.689948892900459e-05</v>
       </c>
       <c r="P23" t="n">
-        <v>0.05962437876316531</v>
+        <v>0.007972374561553161</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.012055731148548e-09</v>
+        <v>1.353219527524421e-10</v>
       </c>
     </row>
     <row r="24">
@@ -1787,52 +1787,52 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>17.31787174163588</v>
+        <v>18.79945826375223</v>
       </c>
       <c r="C25" t="n">
-        <v>4315.62191</v>
+        <v>4684.833979</v>
       </c>
       <c r="D25" t="n">
-        <v>122613.8360828903</v>
+        <v>133103.7513378137</v>
       </c>
       <c r="E25" t="n">
-        <v>0.3168213174358385</v>
+        <v>0.343926160388541</v>
       </c>
       <c r="F25" t="n">
-        <v>3.731477745606923</v>
+        <v>4.050714844596206</v>
       </c>
       <c r="G25" t="n">
-        <v>38.05309473222793</v>
+        <v>41.3086305810435</v>
       </c>
       <c r="H25" t="n">
-        <v>1.881294351846978e-06</v>
+        <v>2.042243710833674e-06</v>
       </c>
       <c r="I25" t="n">
-        <v>4.650472670484313e-05</v>
+        <v>5.048332045634596e-05</v>
       </c>
       <c r="J25" t="n">
-        <v>792.1338600625552</v>
+        <v>859.9028601042323</v>
       </c>
       <c r="K25" t="n">
-        <v>18558.76870254552</v>
+        <v>20146.51701174791</v>
       </c>
       <c r="L25" t="n">
-        <v>0.03230886659700927</v>
+        <v>0.03507296960049198</v>
       </c>
       <c r="M25" t="n">
-        <v>0.0001237092831275729</v>
+        <v>0.000134292916571504</v>
       </c>
       <c r="N25" t="n">
-        <v>23.53111539488588</v>
+        <v>25.54426019348191</v>
       </c>
       <c r="O25" t="n">
-        <v>1798.278941069074</v>
+        <v>1952.126127481018</v>
       </c>
       <c r="P25" t="n">
-        <v>276571.6660052663</v>
+        <v>300233.052281012</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.001775736734938474</v>
+        <v>0.00192765538017168</v>
       </c>
     </row>
     <row r="26">
@@ -1897,52 +1897,52 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3.647670891497241e-07</v>
+        <v>7.014751714419216e-08</v>
       </c>
       <c r="C27" t="n">
-        <v>-2.599999999999465e-05</v>
+        <v>-5.000000000000001e-06</v>
       </c>
       <c r="D27" t="n">
-        <v>0.002853129328914682</v>
+        <v>0.0005486787170990902</v>
       </c>
       <c r="E27" t="n">
-        <v>1.034367464782789e-08</v>
+        <v>1.989168201505773e-09</v>
       </c>
       <c r="F27" t="n">
-        <v>1.210421105345467e-07</v>
+        <v>2.327732894895608e-08</v>
       </c>
       <c r="G27" t="n">
-        <v>7.544788634263474e-07</v>
+        <v>1.450920891204813e-07</v>
       </c>
       <c r="H27" t="n">
-        <v>6.685692513316597e-14</v>
+        <v>1.285710098714995e-14</v>
       </c>
       <c r="I27" t="n">
-        <v>1.433102388251003e-12</v>
+        <v>2.755966131252496e-13</v>
       </c>
       <c r="J27" t="n">
-        <v>4.677559194042641e-06</v>
+        <v>8.995306142391547e-07</v>
       </c>
       <c r="K27" t="n">
-        <v>0.0009421895433396231</v>
+        <v>0.0001811902967961187</v>
       </c>
       <c r="L27" t="n">
-        <v>1.703010954081896e-09</v>
+        <v>3.275021065542782e-10</v>
       </c>
       <c r="M27" t="n">
-        <v>2.204981956791264e-12</v>
+        <v>4.240349916907149e-13</v>
       </c>
       <c r="N27" t="n">
-        <v>2.032297374461096e-07</v>
+        <v>3.90826418165676e-08</v>
       </c>
       <c r="O27" t="n">
-        <v>0.0001312354886585502</v>
+        <v>2.523759397280331e-05</v>
       </c>
       <c r="P27" t="n">
-        <v>0.0003983572006723338</v>
+        <v>7.660715397546457e-05</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.221071920556142e-12</v>
+        <v>8.117446001071175e-13</v>
       </c>
     </row>
     <row r="28">
@@ -2282,52 +2282,52 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>9.738669048691683</v>
+        <v>9.73866941783737</v>
       </c>
       <c r="C34" t="n">
-        <v>-16198.327606</v>
+        <v>-16198.32822</v>
       </c>
       <c r="D34" t="n">
-        <v>32714.61447024841</v>
+        <v>32714.6157103007</v>
       </c>
       <c r="E34" t="n">
-        <v>0.1354234697126621</v>
+        <v>0.1354234748459087</v>
       </c>
       <c r="F34" t="n">
-        <v>9.828499607816944</v>
+        <v>9.828499980367672</v>
       </c>
       <c r="G34" t="n">
-        <v>41.4706205276261</v>
+        <v>41.47062209957608</v>
       </c>
       <c r="H34" t="n">
-        <v>-1.477949852198418e-07</v>
+        <v>-1.477949908220325e-07</v>
       </c>
       <c r="I34" t="n">
-        <v>-4.877994049322413e-05</v>
+        <v>-4.877994234223497e-05</v>
       </c>
       <c r="J34" t="n">
-        <v>32.8010439578571</v>
+        <v>32.80104520118552</v>
       </c>
       <c r="K34" t="n">
-        <v>90289.07594644159</v>
+        <v>90289.07936886232</v>
       </c>
       <c r="L34" t="n">
-        <v>0.008231832802713078</v>
+        <v>0.008231833114741915</v>
       </c>
       <c r="M34" t="n">
-        <v>8.804502100157867e-05</v>
+        <v>8.804502433893817e-05</v>
       </c>
       <c r="N34" t="n">
-        <v>2.81445275192981</v>
+        <v>2.814452858612057</v>
       </c>
       <c r="O34" t="n">
-        <v>1603.990549899605</v>
+        <v>1603.990610699104</v>
       </c>
       <c r="P34" t="n">
-        <v>5186.944171642876</v>
+        <v>5186.94436825476</v>
       </c>
       <c r="Q34" t="n">
-        <v>5.750600178235117e-05</v>
+        <v>5.750600396212466e-05</v>
       </c>
     </row>
     <row r="35">
@@ -2337,52 +2337,52 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3.865563770069075</v>
+        <v>3.865563742740678</v>
       </c>
       <c r="C35" t="n">
-        <v>-7496.776408</v>
+        <v>-7496.776355000001</v>
       </c>
       <c r="D35" t="n">
-        <v>46707.24478812671</v>
+        <v>46707.24445792026</v>
       </c>
       <c r="E35" t="n">
-        <v>0.08591938074890708</v>
+        <v>0.08591938014148238</v>
       </c>
       <c r="F35" t="n">
-        <v>4.887984717240082</v>
+        <v>4.887984682683471</v>
       </c>
       <c r="G35" t="n">
-        <v>15.53472384342825</v>
+        <v>15.53472373360233</v>
       </c>
       <c r="H35" t="n">
-        <v>4.382509668288558e-07</v>
+        <v>4.382509637305507e-07</v>
       </c>
       <c r="I35" t="n">
-        <v>1.922019122785829e-05</v>
+        <v>1.922019109197721e-05</v>
       </c>
       <c r="J35" t="n">
-        <v>15.79322105594098</v>
+        <v>15.79322094428757</v>
       </c>
       <c r="K35" t="n">
-        <v>95253.83661854056</v>
+        <v>95253.83594512401</v>
       </c>
       <c r="L35" t="n">
-        <v>0.004707031393995671</v>
+        <v>0.004707031360718346</v>
       </c>
       <c r="M35" t="n">
-        <v>3.517297143792982e-05</v>
+        <v>3.517297118926728e-05</v>
       </c>
       <c r="N35" t="n">
-        <v>1.267828319181971</v>
+        <v>1.267828310218798</v>
       </c>
       <c r="O35" t="n">
-        <v>1307.360761728537</v>
+        <v>1307.360752485881</v>
       </c>
       <c r="P35" t="n">
-        <v>2683.327594520175</v>
+        <v>2683.327575549839</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.103069521997721e-05</v>
+        <v>3.103069500059934e-05</v>
       </c>
     </row>
     <row r="36">
@@ -2392,52 +2392,52 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>4.18674228381886e-07</v>
+        <v>2.517518236021685e-08</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.00152999999999997</v>
+        <v>-9.199999999999405e-05</v>
       </c>
       <c r="D36" t="n">
-        <v>0.005228089256430437</v>
+        <v>0.0003143687657461298</v>
       </c>
       <c r="E36" t="n">
-        <v>4.986116670864566e-08</v>
+        <v>2.998187802088363e-09</v>
       </c>
       <c r="F36" t="n">
-        <v>1.04463566448772e-06</v>
+        <v>6.281469355089274e-08</v>
       </c>
       <c r="G36" t="n">
-        <v>1.61888640041673e-06</v>
+        <v>9.734480316230883e-08</v>
       </c>
       <c r="H36" t="n">
-        <v>1.934570382182698e-13</v>
+        <v>1.163271079482354e-14</v>
       </c>
       <c r="I36" t="n">
-        <v>-7.636079881825543e-13</v>
+        <v>-4.591629732862212e-14</v>
       </c>
       <c r="J36" t="n">
-        <v>2.662865690112315e-06</v>
+        <v>1.601200284250471e-07</v>
       </c>
       <c r="K36" t="n">
-        <v>0.04269197058720844</v>
+        <v>0.002567098884982354</v>
       </c>
       <c r="L36" t="n">
-        <v>8.461006898938034e-10</v>
+        <v>5.087664279099767e-11</v>
       </c>
       <c r="M36" t="n">
-        <v>4.565500943155781e-12</v>
+        <v>2.745268540982438e-13</v>
       </c>
       <c r="N36" t="n">
-        <v>2.944602314099489e-07</v>
+        <v>1.770610541811378e-08</v>
       </c>
       <c r="O36" t="n">
-        <v>2.335295363556729e-05</v>
+        <v>1.404229891811826e-06</v>
       </c>
       <c r="P36" t="n">
-        <v>0.0004773132652187404</v>
+        <v>2.870118980400141e-05</v>
       </c>
       <c r="Q36" t="n">
-        <v>5.752881052732055e-12</v>
+        <v>3.459248737590362e-13</v>
       </c>
     </row>
   </sheetData>
